--- a/data/calibrations/recalage parc immobilier.xlsx
+++ b/data/calibrations/recalage parc immobilier.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\callonnecg\Documents\Github\ThreeME\data\calibrations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ThreeME\data\calibrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BD575F-7E55-4B62-980B-B29BFA9FEFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA9B845-D2B6-4892-BE6A-BF5A2EF05F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{F3B8202A-200E-4C94-BB50-F6C7EC74A6D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F3B8202A-200E-4C94-BB50-F6C7EC74A6D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -4248,6 +4248,8 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="technical_coef_var_ams2"/>
+      <sheetName val="technical_coef_var_ams"/>
       <sheetName val="Legend"/>
       <sheetName val="BaselineHypotheses"/>
       <sheetName val="Supply_Use_dom"/>
@@ -4285,109 +4287,111 @@
       <sheetName val="M_footprint"/>
       <sheetName val="imports"/>
       <sheetName val="ThreeME V1_V2"/>
-      <sheetName val="technical_coef_variation"/>
-      <sheetName val="technical_coef_variation_2"/>
+      <sheetName val="technical_coef_var"/>
+      <sheetName val="technical_coef_var_2"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23">
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25">
         <row r="112">
           <cell r="C112">
-            <v>93490.199912522992</v>
+            <v>87751.618720638086</v>
           </cell>
           <cell r="D112">
-            <v>94991.215312380547</v>
+            <v>89160.499343263247</v>
           </cell>
           <cell r="E112">
-            <v>96516.33</v>
+            <v>90592</v>
           </cell>
           <cell r="F112">
-            <v>97673.266485</v>
+            <v>94648.266136827398</v>
           </cell>
           <cell r="G112">
-            <v>95467.46020370051</v>
+            <v>95762.724587009448</v>
           </cell>
           <cell r="H112">
-            <v>89492.331932913148</v>
+            <v>91338.839657598044</v>
           </cell>
           <cell r="I112">
-            <v>86947.123869565607</v>
+            <v>92842.624494560863</v>
           </cell>
           <cell r="J112">
-            <v>89045.778914170281</v>
+            <v>93318.268879765921</v>
           </cell>
           <cell r="K112">
-            <v>87334.761178873945</v>
+            <v>92489.468976352844</v>
           </cell>
           <cell r="L112">
-            <v>84337.494080065313</v>
+            <v>90798.539210687566</v>
           </cell>
           <cell r="M112">
-            <v>79853.226005545759</v>
+            <v>90214.103201844002</v>
           </cell>
           <cell r="N112">
-            <v>77309.701338006067</v>
+            <v>89458.218290576231</v>
           </cell>
           <cell r="O112">
-            <v>78523.708283973741</v>
+            <v>89952.8511135187</v>
           </cell>
           <cell r="P112">
-            <v>82897.372669924283</v>
+            <v>90856.473477041116</v>
           </cell>
           <cell r="Q112">
-            <v>84232.870917019492</v>
+            <v>91823.240132446401</v>
           </cell>
           <cell r="R112">
-            <v>84622.789372484607</v>
+            <v>93114.179953723637</v>
           </cell>
           <cell r="S112">
-            <v>78173.867846384412</v>
+            <v>94430.836424917245</v>
           </cell>
           <cell r="T112">
-            <v>87179.739637432285</v>
+            <v>95639.839113910901</v>
           </cell>
           <cell r="U112">
-            <v>85067.185932388864</v>
+            <v>96845.365622296798</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -14069,79 +14073,79 @@
       </c>
       <c r="B42">
         <f>[1]exo_realistic_1!C112</f>
-        <v>93490.199912522992</v>
+        <v>87751.618720638086</v>
       </c>
       <c r="C42">
         <f>[1]exo_realistic_1!D112</f>
-        <v>94991.215312380547</v>
+        <v>89160.499343263247</v>
       </c>
       <c r="D42">
         <f>[1]exo_realistic_1!E112</f>
-        <v>96516.33</v>
+        <v>90592</v>
       </c>
       <c r="E42">
         <f>[1]exo_realistic_1!F112</f>
-        <v>97673.266485</v>
+        <v>94648.266136827398</v>
       </c>
       <c r="F42">
         <f>[1]exo_realistic_1!G112</f>
-        <v>95467.46020370051</v>
+        <v>95762.724587009448</v>
       </c>
       <c r="G42">
         <f>[1]exo_realistic_1!H112</f>
-        <v>89492.331932913148</v>
+        <v>91338.839657598044</v>
       </c>
       <c r="H42">
         <f>[1]exo_realistic_1!I112</f>
-        <v>86947.123869565607</v>
+        <v>92842.624494560863</v>
       </c>
       <c r="I42">
         <f>[1]exo_realistic_1!J112</f>
-        <v>89045.778914170281</v>
+        <v>93318.268879765921</v>
       </c>
       <c r="J42">
         <f>[1]exo_realistic_1!K112</f>
-        <v>87334.761178873945</v>
+        <v>92489.468976352844</v>
       </c>
       <c r="K42">
         <f>[1]exo_realistic_1!L112</f>
-        <v>84337.494080065313</v>
+        <v>90798.539210687566</v>
       </c>
       <c r="L42">
         <f>[1]exo_realistic_1!M112</f>
-        <v>79853.226005545759</v>
+        <v>90214.103201844002</v>
       </c>
       <c r="M42">
         <f>[1]exo_realistic_1!N112</f>
-        <v>77309.701338006067</v>
+        <v>89458.218290576231</v>
       </c>
       <c r="N42">
         <f>[1]exo_realistic_1!O112</f>
-        <v>78523.708283973741</v>
+        <v>89952.8511135187</v>
       </c>
       <c r="O42">
         <f>[1]exo_realistic_1!P112</f>
-        <v>82897.372669924283</v>
+        <v>90856.473477041116</v>
       </c>
       <c r="P42">
         <f>[1]exo_realistic_1!Q112</f>
-        <v>84232.870917019492</v>
+        <v>91823.240132446401</v>
       </c>
       <c r="Q42">
         <f>[1]exo_realistic_1!R112</f>
-        <v>84622.789372484607</v>
+        <v>93114.179953723637</v>
       </c>
       <c r="R42">
         <f>[1]exo_realistic_1!S112</f>
-        <v>78173.867846384412</v>
+        <v>94430.836424917245</v>
       </c>
       <c r="S42">
         <f>[1]exo_realistic_1!T112</f>
-        <v>87179.739637432285</v>
+        <v>95639.839113910901</v>
       </c>
       <c r="T42">
         <f>[1]exo_realistic_1!U112</f>
-        <v>85067.185932388864</v>
+        <v>96845.365622296798</v>
       </c>
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
